--- a/data/kkp/fish_book_kkp.xlsx
+++ b/data/kkp/fish_book_kkp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/faridannam/Desktop/kkp_catch_fishery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6E9DAD-EAB3-4E45-B1A2-C143055AD497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554E916C-36ED-164F-A145-CD0A9DE5AFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fish Book KKP" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="519">
   <si>
     <t>fish_group</t>
   </si>
@@ -88,6 +88,9 @@
     <t>Capture</t>
   </si>
   <si>
+    <t>siganus guttatus</t>
+  </si>
+  <si>
     <t>siganus</t>
   </si>
   <si>
@@ -106,19 +109,19 @@
     <t>animalia</t>
   </si>
   <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=126071</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Baronang</t>
+    <t>https://ppid.kkp.go.id/media/uploads/document_information_public/signed_file-LAPORAN_STATISTIK_2024_converted.pdf_cle_tZRnCWD.pdf#page=19</t>
   </si>
   <si>
     <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=308</t>
   </si>
   <si>
-    <t>https://id.wikipedia.org/wiki/Baronang</t>
-  </si>
-  <si>
-    <t>General name for rabbitfishes; FishBase, ACIAR and Wikipedia all use it for several Siganus species.</t>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=273913</t>
+  </si>
+  <si>
+    <t>https://id.wikipedia.org/wiki/Baronang_totol</t>
+  </si>
+  <si>
+    <t>Golden rabbitfish. KKP's statistical classification defines 'ikan beronang' as S. guttatus (S. canaliculatus is 'beronang lingkis'); ACIAR lists it under baronang; Indonesian Wikipedia calls it baronang totol.</t>
   </si>
   <si>
     <t>BARONANG ANGIN</t>
@@ -145,19 +148,28 @@
     <t>BARONANG HITAM</t>
   </si>
   <si>
-    <t>siganus fuscescens</t>
-  </si>
-  <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=273912</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Black%20rabbitfish</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/wiki/Siganus_fuscescens</t>
-  </si>
-  <si>
-    <t>Best guess: 'hitam' (black) matches the English name black rabbitfish, which FishBase and English Wikipedia give for S. fuscescens. No Indonesian source uses baronang hitam for a rabbitfish; ACIAR uses it for a sweetlips.</t>
+    <t>plectorhinchus schotaf</t>
+  </si>
+  <si>
+    <t>plectorhinchus</t>
+  </si>
+  <si>
+    <t>haemulidae</t>
+  </si>
+  <si>
+    <t>eupercaria</t>
+  </si>
+  <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=210</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218551</t>
+  </si>
+  <si>
+    <t>https://www.fishbase.se/summary/Plectorhinchus-schotaf.html</t>
+  </si>
+  <si>
+    <t>ACIAR lists 'Baronang Hitam, Kaci-kaci' for this sweetlips (Haemulidae). No other source uses the name, and KKP places it in the BARONANG (rabbitfish) group.</t>
   </si>
   <si>
     <t>BARONANG KUNYIT</t>
@@ -196,15 +208,15 @@
     <t>carangiformes</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=174</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218431</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Bawal%20hitam</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=174</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Bawal_hitam</t>
   </si>
   <si>
@@ -226,7 +238,7 @@
     <t>labridae</t>
   </si>
   <si>
-    <t>eupercaria</t>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=264</t>
   </si>
   <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218941</t>
@@ -235,9 +247,6 @@
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kakatua%20putih</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=264</t>
-  </si>
-  <si>
     <t>https://www.melekperikanan.com/2022/07/ikan-bayeman-kakatua-putih-atau-floral.html</t>
   </si>
   <si>
@@ -262,34 +271,40 @@
     <t>mulliformes</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=244</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218658</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Biji%20nangka%20karang</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=244</t>
-  </si>
-  <si>
     <t>FishBase (Indonesia) and ACIAR agree.</t>
   </si>
   <si>
     <t>KUNIRAN; BIJI NANGKA</t>
   </si>
   <si>
-    <t>mulloidichthys vanicolensis</t>
-  </si>
-  <si>
-    <t>mulloidichthys</t>
-  </si>
-  <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218648</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Biji%20nangka</t>
-  </si>
-  <si>
-    <t>FishBase lists biji nangka for M. vanicolensis and M. flavolineatus (Malaysia); its kuniran entries are Upeneus. Wikipedia's page for the name is the Atlantic M. martinicus and is not used.</t>
+    <t>upeneus moluccensis</t>
+  </si>
+  <si>
+    <t>upeneus</t>
+  </si>
+  <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=246</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=126989</t>
+  </si>
+  <si>
+    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Bidji%20nangka</t>
+  </si>
+  <si>
+    <t>https://id.wikipedia.org/wiki/Kuniran</t>
+  </si>
+  <si>
+    <t>Goldband goatfish, named after Maluku. FishBase calls it bidji nangka and ikan kunir, Wikipedia's kuniran page is this species; ACIAR lists it as dayah jenggot.</t>
   </si>
   <si>
     <t>CAKALANG</t>
@@ -307,15 +322,15 @@
     <t>scombriformes</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=328</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=127018</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Cakalang</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=328</t>
-  </si>
-  <si>
     <t>https://iotc.org/sites/default/files/documents/2015/09/Tuna_-_Indonesian.pdf#page=11</t>
   </si>
   <si>
@@ -325,19 +340,25 @@
     <t>CUMI-CUMI</t>
   </si>
   <si>
+    <t>loliginidae</t>
+  </si>
+  <si>
+    <t>myopsida</t>
+  </si>
+  <si>
     <t>cephalopoda</t>
   </si>
   <si>
     <t>mollusca</t>
   </si>
   <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=11707</t>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=11734</t>
   </si>
   <si>
     <t>https://id.wikipedia.org/wiki/Cumi-cumi</t>
   </si>
   <si>
-    <t>Squid, not a fish. WoRMS class for squids, cuttlefishes and octopuses; Wikipedia's Teuthida is no longer an accepted name.</t>
+    <t>Inshore squids (Uroteuthis, Loligo, Sepioteuthis), the squid sold as cumi-cumi; cuttlefish and octopus are not in the KKP file. Not a fish, so not in ACIAR.</t>
   </si>
   <si>
     <t>EKOR KUNING</t>
@@ -352,34 +373,34 @@
     <t>caesionidae</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=202</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=278536</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Ekor%20kuning</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=202</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Caesio_cuning</t>
   </si>
   <si>
     <t>LOLOSI PAPAN</t>
   </si>
   <si>
-    <t>caesio teres</t>
-  </si>
-  <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=219996</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Ekor%20kuning%20pisang</t>
-  </si>
-  <si>
-    <t>https://id.wikipedia.org/wiki/Lolosi_cantik</t>
-  </si>
-  <si>
-    <t>Fusilier. No source uses 'lolosi papan'; Wikipedia calls C. teres lolosi cantik, FishBase and ACIAR ekor kuning pisang. Lolosi is the Maluku name for fusiliers. Other source: https://ojs3.unpatti.ac.id/index.php/triton/article/view/6632</t>
+    <t>caesio xanthonota</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=219994</t>
+  </si>
+  <si>
+    <t>https://id.wikipedia.org/wiki/Caesio_xanthonota</t>
+  </si>
+  <si>
+    <t>https://ojs3.unpatti.ac.id/index.php/triton/article/view/6632</t>
+  </si>
+  <si>
+    <t>Yellowback fusilier. ACIAR lists it as ekor kuning / antuan; FishBase gives antuan and ekor kuning pisang for Indonesia. No source uses 'lolosi papan'; lolosi is the Maluku name for fusiliers. Other source: https://www.fishbase.se/summary/Caesio-xanthonota.html</t>
   </si>
   <si>
     <t>JULUNG-JULUNG</t>
@@ -415,22 +436,28 @@
     <t>A needlefish. Wikipedia and Indonesian fisheries studies agree. ACIAR uses 'cendro' for a lizardfish. Other source: https://www.fishbase.se/summary/Tylosurus-crocodilus.html</t>
   </si>
   <si>
+    <t>hemiramphus far</t>
+  </si>
+  <si>
+    <t>hemiramphus</t>
+  </si>
+  <si>
     <t>hemiramphidae</t>
   </si>
   <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=125453</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Julung-julung</t>
-  </si>
-  <si>
     <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=100</t>
   </si>
   <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=126389</t>
+  </si>
+  <si>
     <t>https://id.wikipedia.org/wiki/Julung-julung</t>
   </si>
   <si>
-    <t>Halfbeaks. ACIAR applies the name to at least five species, so kept at family.</t>
+    <t>https://journals.sangia.org/ISLE/article/view/57</t>
+  </si>
+  <si>
+    <t>Blackbarred halfbeak. ACIAR lists it as julung-julung; Ternate and Tidore studies of ikan julung use this species. Other source: https://www.researchgate.net/publication/323033496_Pengaruh_waktu_dan_SPL_terhadap_jumlah_hasil_tangkapan_ikan_julung_Hemirhamphus_far; https://www.fishbase.se/summary/Hemiramphus-far.html</t>
   </si>
   <si>
     <t>KACI-KACI</t>
@@ -442,21 +469,12 @@
     <t>plectorhinchus gibbosus</t>
   </si>
   <si>
-    <t>plectorhinchus</t>
-  </si>
-  <si>
-    <t>haemulidae</t>
-  </si>
-  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218539</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kaci%20kakap</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=210</t>
-  </si>
-  <si>
     <t>https://fishider.org/id/guide/osteichthyes/haemulidae/plectorhinchus/plectorhinchus-gibbosus</t>
   </si>
   <si>
@@ -472,12 +490,12 @@
     <t>lutjanidae</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=188</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=159791</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=188</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Kakap</t>
   </si>
   <si>
@@ -514,12 +532,12 @@
     <t>lutjanus malabaricus</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=192</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218481</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=192</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Kakap_merah</t>
   </si>
   <si>
@@ -532,19 +550,16 @@
     <t>KAKAP MERAH UTARA</t>
   </si>
   <si>
-    <t>lutjanus campechanus</t>
-  </si>
-  <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=159795</t>
-  </si>
-  <si>
-    <t>https://id.wikipedia.org/wiki/Kakap_merah_utara</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/summary/Lutjanus-campechanus.html</t>
-  </si>
-  <si>
-    <t>Wikipedia only. L. campechanus lives in the Gulf of Mexico, so the KKP category follows the name rather than a local fish.</t>
+    <t>lutjanus bohar</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218479</t>
+  </si>
+  <si>
+    <t>https://www.fishbase.se/summary/Lutjanus-bohar.html</t>
+  </si>
+  <si>
+    <t>Two-spot red snapper, the ikan merah of eastern Indonesian reef fisheries; ACIAR calls it kakap merah. Used in place of the Gulf of Mexico species that Wikipedia attaches to this KKP name.</t>
   </si>
   <si>
     <t>KAKAP PUTIH; BARAMUNDI</t>
@@ -562,15 +577,15 @@
     <t>carangaria</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=122</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=278957</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kakap%20putih</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=122</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Kakap_putih</t>
   </si>
   <si>
@@ -586,15 +601,15 @@
     <t>pristipomoides</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=200</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218507</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kerisi%20bali</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=200</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Kurisi_bali</t>
   </si>
   <si>
@@ -610,15 +625,15 @@
     <t>pinjalo</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=198</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218506</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Penyalo</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=198</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Pinjalo</t>
   </si>
   <si>
@@ -634,15 +649,15 @@
     <t>subfamily</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=284</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=151787</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kakatua</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=284</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Ikan_kakatua</t>
   </si>
   <si>
@@ -658,30 +673,30 @@
     <t>scarus</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=286</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=219127</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kakatua%20biru</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=286</t>
-  </si>
-  <si>
     <t>KEMBUNG</t>
   </si>
   <si>
     <t>rastrelliger</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=330</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=126061</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kembung</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=330</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Ikan_kembung</t>
   </si>
   <si>
@@ -712,15 +727,15 @@
     <t>perciformes</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=136</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=1776907</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kerapu</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=136</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Kerapu</t>
   </si>
   <si>
@@ -739,12 +754,12 @@
     <t>scorpaenidae</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=116</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=277531</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=116</t>
-  </si>
-  <si>
     <t>https://www.fishbase.se/summary/Scorpaenopsis-oxycephala.html</t>
   </si>
   <si>
@@ -760,15 +775,15 @@
     <t>chromileptes</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=130</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=401295</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kerapu%20tikus</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=130</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Kerapu_bebek</t>
   </si>
   <si>
@@ -778,21 +793,24 @@
     <t>KERAPU KARANG</t>
   </si>
   <si>
-    <t>cephalopholis cyanostigma</t>
+    <t>cephalopholis boenak</t>
   </si>
   <si>
     <t>cephalopholis</t>
   </si>
   <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=279147</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kerapu%20karang</t>
-  </si>
-  <si>
     <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=126</t>
   </si>
   <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218182</t>
+  </si>
+  <si>
+    <t>https://www.fishbase.se/summary/Cephalopholis-boenak.html</t>
+  </si>
+  <si>
+    <t>Chocolate hind. KKP's statistical classification defines kerapu karang as C. boenak (in that part of the list the scientific name is printed one line below the Indonesian name); ACIAR lists it; FishBase gives kerapu and kerapu batu for it in Indonesia.</t>
+  </si>
+  <si>
     <t>KERAPU LUMPUR</t>
   </si>
   <si>
@@ -820,16 +838,19 @@
     <t>cephalopholis sonnerati</t>
   </si>
   <si>
+    <t>https://fisheryprogress.org/sites/default/files/documents_actions/Kepmen%20KP%20123%20Tahun%202021%20RPP%20Kakap%20Kerapu.pdf#page=47</t>
+  </si>
+  <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=128</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218183</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kerapu%20merah</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=128</t>
-  </si>
-  <si>
-    <t>Tomato grouper. FishBase lists kerapu merah (Malaysia) for C. sonnerati and also for Plectropomus leopardus, which KKP reports separately; ACIAR calls it keyapu tomat.</t>
+    <t>Tomato hind. KKP's snapper-grouper management plan (Kepmen KP 123/2021) lists C. sonnerati as kerapu tomat; FishBase lists kerapu merah for it; ACIAR lists it. Not in KKP's statistical classification.</t>
   </si>
   <si>
     <t>KERAPU MERAH BINTIK BIRU</t>
@@ -841,15 +862,15 @@
     <t>plectropomus</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=144</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218261</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kerapu%20sunu</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=144</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Kerapu_sunuk</t>
   </si>
   <si>
@@ -862,28 +883,31 @@
     <t>KERISI</t>
   </si>
   <si>
+    <t>nemipterus hexodon</t>
+  </si>
+  <si>
     <t>nemipterus</t>
   </si>
   <si>
     <t>nemipteridae</t>
   </si>
   <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=205457</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Kurisi</t>
-  </si>
-  <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=226</t>
+    <t>https://ppid.kkp.go.id/media/uploads/document_information_public/signed_file-LAPORAN_STATISTIK_2024_converted.pdf_cle_tZRnCWD.pdf#page=18</t>
+  </si>
+  <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=224</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=278124</t>
   </si>
   <si>
     <t>https://id.wikipedia.org/wiki/Kurisi</t>
   </si>
   <si>
-    <t>Spelling variant of KURISI (one row, Kota Ternate).</t>
-  </si>
-  <si>
-    <t>Threadfin breams; FishBase and ACIAR list several Nemipterus species under this name.</t>
+    <t>Spelling variant of KURISI (one row, Kota Ternate); same species.</t>
+  </si>
+  <si>
+    <t>Ornate threadfin bream. KKP's statistical classification defines kurisi as N. hexodon (in that part of the list the scientific name is printed one line below the Indonesian name); ACIAR lists it; FishBase gives krisi for it in Indonesia.</t>
   </si>
   <si>
     <t>nemipterus balinensis</t>
@@ -892,9 +916,6 @@
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=278118</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=224</t>
-  </si>
-  <si>
     <t>https://www.melekperikanan.com/2022/02/ikan-kurisi-atau-balinese-threadfin.html</t>
   </si>
   <si>
@@ -907,16 +928,22 @@
     <t>KUWE</t>
   </si>
   <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=125523</t>
-  </si>
-  <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=168</t>
+    <t>caranx</t>
+  </si>
+  <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=170</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=125936</t>
   </si>
   <si>
     <t>https://id.wikipedia.org/wiki/Kuwe_gerong</t>
   </si>
   <si>
-    <t>Trevallies. ACIAR uses kwee for Caranx, Carangoides, Alepes and Gnathanodon, so kept at family.</t>
+    <t>https://www.researchgate.net/publication/392857601_Keanekaragaman_Hasil_Tangkapan_Hand_Line_di_Pelabuhan_Perikanan_Nusantara_Ternate</t>
+  </si>
+  <si>
+    <t>Trevallies. Ternate landings record kuwe as Caranx, and KKP's other kuwe names are Caranx species; ACIAR also uses kwee for Carangoides and others.</t>
   </si>
   <si>
     <t>KUWE SIRIP BIRU</t>
@@ -925,15 +952,9 @@
     <t>caranx melampygus</t>
   </si>
   <si>
-    <t>caranx</t>
-  </si>
-  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218419</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=170</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Kuwe_sirip_biru</t>
   </si>
   <si>
@@ -946,16 +967,19 @@
     <t>KUWE SIRIP KUNING</t>
   </si>
   <si>
-    <t>caranx ignobilis</t>
-  </si>
-  <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218414</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Yellow-fin%20trevally</t>
-  </si>
-  <si>
-    <t>Best guess: FishBase lists yellow-fin trevally for C. ignobilis and ACIAR notes its yellow fins in muddy coastal waters. No Indonesian source uses kuwe sirip kuning; C. heberi and C. sexfasciatus also have yellow fins.</t>
+    <t>caranx heberi</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218403</t>
+  </si>
+  <si>
+    <t>https://id.wikipedia.org/wiki/Kuwe_tengguli</t>
+  </si>
+  <si>
+    <t>https://www.fishbase.se/summary/Caranx-heberi.html</t>
+  </si>
+  <si>
+    <t>Blacktip trevally, a Caranx with yellow fins. Not in ACIAR. Indonesian Wikipedia (kuwe tengguli) describes its yellow fins; FishBase records it for Indonesia. No source uses kuwe sirip kuning.</t>
   </si>
   <si>
     <t>LAYANG</t>
@@ -964,15 +988,15 @@
     <t>decapterus</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=172</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=125937</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Layang</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=172</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Layang_(ikan)</t>
   </si>
   <si>
@@ -1054,27 +1078,36 @@
     <t>LAYUR</t>
   </si>
   <si>
-    <t>Same as CENDRO under JULUNG-JULUNG. Other source: https://www.fishbase.se/summary/Tylosurus-crocodilus.html</t>
+    <t>trichiurus auriga</t>
+  </si>
+  <si>
+    <t>trichiurus</t>
+  </si>
+  <si>
+    <t>trichiuridae</t>
+  </si>
+  <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=326</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=219706</t>
+  </si>
+  <si>
+    <t>https://www.fishbase.se/summary/Trichiurus-auriga.html</t>
+  </si>
+  <si>
+    <t>Pearly hairtail, a deep-water hairtail of the Indo-West Pacific including Indonesia, so that CENDRO under LAYUR is a hairtail distinct from Trichiurus lepturus. ACIAR lists two unnamed Trichiurus species as layur. In Maluku, cendro is otherwise the local name of the needlefish (see the JULUNG-JULUNG group).</t>
   </si>
   <si>
     <t>trichiurus lepturus</t>
   </si>
   <si>
-    <t>trichiurus</t>
-  </si>
-  <si>
-    <t>trichiuridae</t>
-  </si>
-  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=127089</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Layur</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=326</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Layur</t>
   </si>
   <si>
@@ -1099,12 +1132,12 @@
     <t>clupeiformes</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=80</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=272269</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=80</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Ikan_tembang</t>
   </si>
   <si>
@@ -1126,15 +1159,15 @@
     <t>lethrinidae</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=220</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=212081</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Lencam</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=220</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Lencam</t>
   </si>
   <si>
@@ -1150,15 +1183,15 @@
     <t>pterocaesio</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=204</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=213658</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Pisang-pisang</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=204</t>
-  </si>
-  <si>
     <t>Banana fusilier. FishBase (Indonesia) and ACIAR agree; both also use the name for other fusiliers.</t>
   </si>
   <si>
@@ -1192,12 +1225,12 @@
     <t>atule</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=164</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218384</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=164</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Selar_hijau</t>
   </si>
   <si>
@@ -1216,15 +1249,15 @@
     <t>selaroides</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=176</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=282745</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Selar%20kuning</t>
   </si>
   <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=176</t>
-  </si>
-  <si>
     <t>https://id.wikipedia.org/wiki/Selar_kuning</t>
   </si>
   <si>
@@ -1267,7 +1300,7 @@
     <t>SWANGGI</t>
   </si>
   <si>
-    <t>priacanthus hamrur</t>
+    <t>priacanthus tayenus</t>
   </si>
   <si>
     <t>priacanthus</t>
@@ -1276,19 +1309,16 @@
     <t>priacanthidae</t>
   </si>
   <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=218360</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Gora%20suangi</t>
-  </si>
-  <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=156</t>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=158</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=273768</t>
   </si>
   <si>
     <t>https://id.wikipedia.org/wiki/Ikan_swanggi</t>
   </si>
   <si>
-    <t>FishBase and ACIAR list P. hamrur as gora suangi. Wikipedia gives P. tayenus.</t>
+    <t>Purple-spotted bigeye. KKP's statistical classification defines swanggi as P. tayenus (in that part of the list the scientific name is printed one line below the Indonesian name); ACIAR and Indonesian Wikipedia agree; FishBase gives serinding tembakau for it.</t>
   </si>
   <si>
     <t>TENGGIRI</t>
@@ -1348,22 +1378,25 @@
     <t>TERBANG; TORANI</t>
   </si>
   <si>
+    <t>hirundichthys oxycephalus</t>
+  </si>
+  <si>
+    <t>hirundichthys</t>
+  </si>
+  <si>
     <t>exocoetidae</t>
   </si>
   <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=125452</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Terbang</t>
-  </si>
-  <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=98</t>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=272171</t>
   </si>
   <si>
     <t>https://id.wikipedia.org/wiki/Torani</t>
   </si>
   <si>
-    <t>Flying fishes; ACIAR applies the names to several Cheilopogon and Cypselurus species.</t>
+    <t>https://www.fishbase.se/summary/Hirundichthys-oxycephalus.html</t>
+  </si>
+  <si>
+    <t>Bony flyingfish, the species of the eastern Indonesian flying-fish and roe fisheries. ACIAR lists it as ikan terbang, torani; the names also cover Cheilopogon and Cypselurus species.</t>
   </si>
   <si>
     <t>TERI</t>
@@ -1420,10 +1453,13 @@
     <t>TERI NASI</t>
   </si>
   <si>
+    <t>stolephorus tri</t>
+  </si>
+  <si>
     <t>stolephorus</t>
   </si>
   <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=206924</t>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=275328</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Teri</t>
@@ -1435,12 +1471,57 @@
     <t>https://jurnal.unpad.ac.id/akuatika-indonesia/article/download/32371/16165</t>
   </si>
   <si>
-    <t>Small anchovies of the genus Stolephorus, as in Indonesian fisheries literature; FishBase lists three Stolephorus species under teri.</t>
+    <t>Spined anchovy. FishBase lists it under teri (Indonesia); teri nasi are small Stolephorus in Indonesian fisheries literature. Not in ACIAR.</t>
   </si>
   <si>
     <t>TONGKOL</t>
   </si>
   <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=125559</t>
+  </si>
+  <si>
+    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Tongkol</t>
+  </si>
+  <si>
+    <t>https://id.wikipedia.org/wiki/Skombride</t>
+  </si>
+  <si>
+    <t>Tunas and mackerels. Tongkol is a general word: ACIAR and FishBase use it for Euthynnus affinis and Auxis species, and KKP's own tongkol names span Euthynnus, Auxis and Thunnus. Kept at family.</t>
+  </si>
+  <si>
+    <t>TONGKOL ABU-ABU</t>
+  </si>
+  <si>
+    <t>thunnus tonggol</t>
+  </si>
+  <si>
+    <t>thunnus</t>
+  </si>
+  <si>
+    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=219722</t>
+  </si>
+  <si>
+    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Abu-abu</t>
+  </si>
+  <si>
+    <t>https://iotc.org/sites/default/files/documents/2015/09/Tuna_-_Indonesian.pdf#page=10</t>
+  </si>
+  <si>
+    <t>https://id.wikipedia.org/wiki/Tongkol_abu-abu</t>
+  </si>
+  <si>
+    <t>FishBase (Indonesia), IOTC and Wikipedia agree.</t>
+  </si>
+  <si>
+    <t>TONGKOL BANYAR</t>
+  </si>
+  <si>
+    <t>Indian mackerel. KKP's statistical classification defines banyar as R. kanagurta; ACIAR and FishBase (banjar, banyara) agree. The IOTC card's 'tongkol banyar' (Auxis thazard) is not followed. Same species as KEMBUNG LELAKI.</t>
+  </si>
+  <si>
+    <t>TONGKOL KOMO</t>
+  </si>
+  <si>
     <t>euthynnus affinis</t>
   </si>
   <si>
@@ -1450,66 +1531,6 @@
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=219708</t>
   </si>
   <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Tongkol</t>
-  </si>
-  <si>
-    <t>https://id.wikipedia.org/wiki/Tongkol</t>
-  </si>
-  <si>
-    <t>FishBase (Indonesia), ACIAR and Wikipedia all use tongkol for E. affinis; FishBase and ACIAR also use it for Auxis species.</t>
-  </si>
-  <si>
-    <t>TONGKOL ABU-ABU</t>
-  </si>
-  <si>
-    <t>thunnus tonggol</t>
-  </si>
-  <si>
-    <t>thunnus</t>
-  </si>
-  <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=219722</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Abu-abu</t>
-  </si>
-  <si>
-    <t>https://iotc.org/sites/default/files/documents/2015/09/Tuna_-_Indonesian.pdf#page=10</t>
-  </si>
-  <si>
-    <t>https://id.wikipedia.org/wiki/Tongkol_abu-abu</t>
-  </si>
-  <si>
-    <t>FishBase (Indonesia), IOTC and Wikipedia agree.</t>
-  </si>
-  <si>
-    <t>TONGKOL BANYAR</t>
-  </si>
-  <si>
-    <t>auxis thazard</t>
-  </si>
-  <si>
-    <t>auxis</t>
-  </si>
-  <si>
-    <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=127016</t>
-  </si>
-  <si>
-    <t>https://iotc.org/sites/default/files/documents/2015/09/Tuna_-_Indonesian.pdf#page=13</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/327488153_Perikanan_Tongkol_dan_Daya_Dukungnya_terhadap_Penyediaan_Bahan_Baku_Industri_Pengolahan_di_Pelabuhanratu</t>
-  </si>
-  <si>
-    <t>https://www.fishbase.se/summary/Auxis-thazard.html</t>
-  </si>
-  <si>
-    <t>IOTC lists 'tongkol banyar' for frigate tuna; a KKP journal article agrees. Wikipedia's match is an eastern Pacific species and is not followed.</t>
-  </si>
-  <si>
-    <t>TONGKOL KOMO</t>
-  </si>
-  <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Tongkol%20komo</t>
   </si>
   <si>
@@ -1528,13 +1549,13 @@
     <t>thunnus obesus</t>
   </si>
   <si>
+    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=332</t>
+  </si>
+  <si>
     <t>https://www.marinespecies.org/aphia.php?p=taxdetails&amp;id=127028</t>
   </si>
   <si>
     <t>https://www.fishbase.se/ComNames/CommonNameSearchList.php?CommonName=Tuna%20mata%20besar</t>
-  </si>
-  <si>
-    <t>https://www.aciar.gov.au/sites/default/files/legacy/node/15500/mn155_fishes_of_indonesia_pdf_19137.pdf#page=332</t>
   </si>
   <si>
     <t>https://iotc.org/sites/default/files/documents/2015/09/Tuna_-_Indonesian.pdf#page=6</t>
@@ -1580,7 +1601,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1590,11 +1611,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1610,10 +1626,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1921,16 +1936,18 @@
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="4" width="9" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="9" width="16" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="17" width="60" customWidth="1"/>
+    <col min="14" max="17" width="59.83203125" customWidth="1"/>
     <col min="18" max="18" width="100" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2007,40 +2024,43 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -2048,7 +2068,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -2057,100 +2077,99 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="B4" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="2" t="s">
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="I4" t="s">
         <v>43</v>
       </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="s">
+      <c r="J4" t="s">
         <v>44</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -2158,7 +2177,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -2167,51 +2186,51 @@
         <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -2220,54 +2239,54 @@
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="O6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="P6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="R6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -2276,54 +2295,54 @@
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J7" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="R7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -2332,51 +2351,51 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F8" t="s">
         <v>6</v>
       </c>
       <c r="G8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="O8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P8" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -2385,48 +2404,54 @@
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
         <v>6</v>
       </c>
       <c r="G9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O9" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="P9" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>92</v>
       </c>
       <c r="R9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
@@ -2435,54 +2460,54 @@
         <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F10" t="s">
         <v>6</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="Q10" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="R10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -2491,36 +2516,42 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="I11" t="s">
+        <v>105</v>
+      </c>
+      <c r="J11" t="s">
+        <v>106</v>
       </c>
       <c r="K11" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L11" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="O11" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="R11" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
         <v>19</v>
@@ -2529,110 +2560,110 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F12" t="s">
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H12" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I12" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J12" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="O12" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="P12" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="Q12" t="s">
+        <v>119</v>
+      </c>
+      <c r="R12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>112</v>
       </c>
-      <c r="R12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" t="s">
         <v>114</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="2" t="s">
+      <c r="I13" t="s">
         <v>115</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="J13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" t="s">
         <v>116</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>118</v>
+      <c r="O13" t="s">
+        <v>122</v>
+      </c>
+      <c r="P13" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>124</v>
+      </c>
+      <c r="R13" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -2641,54 +2672,54 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F14" t="s">
         <v>6</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H14" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I14" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="J14" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N14" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="O14" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="P14" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Q14" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="R14" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -2697,104 +2728,110 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="G15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H15" t="s">
+        <v>138</v>
       </c>
       <c r="I15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J15" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="O15" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="P15" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="Q15" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="R15" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="R16" s="2" t="s">
+      <c r="A16" t="s">
         <v>145</v>
+      </c>
+      <c r="B16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>147</v>
+      </c>
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" t="s">
+        <v>44</v>
+      </c>
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O16" t="s">
+        <v>148</v>
+      </c>
+      <c r="P16" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>150</v>
+      </c>
+      <c r="R16" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
         <v>19</v>
@@ -2803,48 +2840,48 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
       </c>
       <c r="H17" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I17" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J17" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N17" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="O17" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="P17" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="R17" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
         <v>19</v>
@@ -2853,51 +2890,51 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F18" t="s">
         <v>6</v>
       </c>
       <c r="G18" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="H18" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="I18" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N18" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O18" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="P18" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="R18" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C19" t="s">
         <v>19</v>
@@ -2906,54 +2943,54 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F19" t="s">
         <v>6</v>
       </c>
       <c r="G19" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H19" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I19" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J19" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O19" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="P19" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="Q19" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="R19" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -2962,51 +2999,51 @@
         <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F20" t="s">
         <v>6</v>
       </c>
       <c r="G20" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="I20" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J20" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N20" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="O20" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="R20" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
@@ -3015,54 +3052,54 @@
         <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F21" t="s">
         <v>6</v>
       </c>
       <c r="G21" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H21" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="I21" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J21" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N21" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="O21" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Q21" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="R21" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
@@ -3071,54 +3108,54 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F22" t="s">
         <v>6</v>
       </c>
       <c r="G22" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H22" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="I22" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J22" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N22" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="O22" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="P22" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Q22" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="R22" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s">
         <v>19</v>
@@ -3127,54 +3164,54 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
       </c>
       <c r="G23" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H23" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I23" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J23" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N23" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="O23" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="P23" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q23" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="R23" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
@@ -3183,48 +3220,48 @@
         <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F24" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I24" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N24" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="O24" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="P24" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Q24" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="R24" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B25" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -3233,51 +3270,51 @@
         <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F25" t="s">
         <v>6</v>
       </c>
       <c r="G25" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H25" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="I25" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J25" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N25" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="O25" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="P25" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="R25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C26" t="s">
         <v>19</v>
@@ -3286,107 +3323,107 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F26" t="s">
         <v>7</v>
       </c>
       <c r="H26" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I26" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J26" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N26" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="O26" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="P26" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q26" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="R26" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B27" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>227</v>
+      </c>
+      <c r="F27" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" t="s">
+        <v>227</v>
+      </c>
+      <c r="H27" t="s">
+        <v>220</v>
+      </c>
+      <c r="I27" t="s">
+        <v>97</v>
+      </c>
+      <c r="J27" t="s">
+        <v>98</v>
+      </c>
+      <c r="K27" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" t="s">
         <v>221</v>
       </c>
-      <c r="C27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" t="s">
-        <v>222</v>
-      </c>
-      <c r="F27" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" t="s">
-        <v>222</v>
-      </c>
-      <c r="H27" t="s">
-        <v>215</v>
-      </c>
-      <c r="I27" t="s">
-        <v>92</v>
-      </c>
-      <c r="J27" t="s">
-        <v>93</v>
-      </c>
-      <c r="K27" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" t="s">
-        <v>223</v>
-      </c>
       <c r="O27" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="P27" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="Q27" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="R27" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C28" t="s">
         <v>19</v>
@@ -3395,102 +3432,101 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F28" t="s">
         <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="J28" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N28" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="O28" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="P28" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>237</v>
+      </c>
+      <c r="R28" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>231</v>
       </c>
-      <c r="Q28" t="s">
-        <v>232</v>
-      </c>
-      <c r="R28" t="s">
+      <c r="B29" t="s">
+        <v>239</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
+        <v>240</v>
+      </c>
+      <c r="F29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" t="s">
+        <v>240</v>
+      </c>
+      <c r="H29" t="s">
+        <v>241</v>
+      </c>
+      <c r="I29" t="s">
+        <v>242</v>
+      </c>
+      <c r="J29" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2" t="s">
-        <v>241</v>
+      <c r="K29" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" t="s">
+        <v>27</v>
+      </c>
+      <c r="N29" t="s">
+        <v>243</v>
+      </c>
+      <c r="O29" t="s">
+        <v>244</v>
+      </c>
+      <c r="P29" t="s">
+        <v>245</v>
+      </c>
+      <c r="R29" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B30" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -3499,54 +3535,54 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F30" t="s">
         <v>6</v>
       </c>
       <c r="G30" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H30" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I30" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="J30" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N30" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="O30" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="P30" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="Q30" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="R30" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B31" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C31" t="s">
         <v>19</v>
@@ -3555,51 +3591,54 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F31" t="s">
         <v>6</v>
       </c>
       <c r="G31" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="H31" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I31" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="J31" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N31" t="s">
-        <v>253</v>
+        <v>28</v>
       </c>
       <c r="O31" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="P31" t="s">
-        <v>255</v>
+        <v>259</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>260</v>
       </c>
       <c r="R31" t="s">
-        <v>82</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B32" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C32" t="s">
         <v>19</v>
@@ -3608,105 +3647,107 @@
         <v>20</v>
       </c>
       <c r="E32" t="s">
+        <v>263</v>
+      </c>
+      <c r="F32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" t="s">
+        <v>263</v>
+      </c>
+      <c r="H32" t="s">
+        <v>264</v>
+      </c>
+      <c r="I32" t="s">
+        <v>232</v>
+      </c>
+      <c r="J32" t="s">
+        <v>233</v>
+      </c>
+      <c r="K32" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" t="s">
+        <v>265</v>
+      </c>
+      <c r="O32" t="s">
+        <v>266</v>
+      </c>
+      <c r="P32" t="s">
+        <v>267</v>
+      </c>
+      <c r="R32" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>231</v>
+      </c>
+      <c r="B33" t="s">
+        <v>269</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>270</v>
+      </c>
+      <c r="F33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33" t="s">
+        <v>270</v>
+      </c>
+      <c r="H33" t="s">
         <v>257</v>
       </c>
-      <c r="F32" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" t="s">
-        <v>257</v>
-      </c>
-      <c r="H32" t="s">
-        <v>258</v>
-      </c>
-      <c r="I32" t="s">
-        <v>227</v>
-      </c>
-      <c r="J32" t="s">
-        <v>228</v>
-      </c>
-      <c r="K32" t="s">
-        <v>24</v>
-      </c>
-      <c r="L32" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N32" t="s">
-        <v>259</v>
-      </c>
-      <c r="O32" t="s">
-        <v>260</v>
-      </c>
-      <c r="P32" t="s">
-        <v>261</v>
-      </c>
-      <c r="R32" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2" t="s">
-        <v>268</v>
+      <c r="I33" t="s">
+        <v>232</v>
+      </c>
+      <c r="J33" t="s">
+        <v>233</v>
+      </c>
+      <c r="K33" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" t="s">
+        <v>27</v>
+      </c>
+      <c r="N33" t="s">
+        <v>271</v>
+      </c>
+      <c r="O33" t="s">
+        <v>272</v>
+      </c>
+      <c r="P33" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>274</v>
+      </c>
+      <c r="R33" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B34" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C34" t="s">
         <v>19</v>
@@ -3715,54 +3756,54 @@
         <v>20</v>
       </c>
       <c r="E34" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F34" t="s">
         <v>6</v>
       </c>
       <c r="G34" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="H34" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="I34" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="J34" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N34" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="O34" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="P34" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="Q34" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="R34" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C35" t="s">
         <v>19</v>
@@ -3771,51 +3812,54 @@
         <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="F35" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="G35" t="s">
+        <v>286</v>
       </c>
       <c r="H35" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="I35" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="J35" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N35" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="O35" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="P35" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="Q35" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="R35" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C36" t="s">
         <v>19</v>
@@ -3824,51 +3868,54 @@
         <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="F36" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="G36" t="s">
+        <v>286</v>
       </c>
       <c r="H36" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="I36" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="J36" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N36" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="O36" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="P36" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="Q36" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="R36" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B37" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C37" t="s">
         <v>19</v>
@@ -3877,54 +3924,54 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
+        <v>295</v>
+      </c>
+      <c r="F37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G37" t="s">
+        <v>295</v>
+      </c>
+      <c r="H37" t="s">
         <v>287</v>
       </c>
-      <c r="F37" t="s">
-        <v>6</v>
-      </c>
-      <c r="G37" t="s">
-        <v>287</v>
-      </c>
-      <c r="H37" t="s">
-        <v>279</v>
-      </c>
       <c r="I37" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="J37" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N37" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O37" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="P37" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="Q37" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="R37" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C38" t="s">
         <v>19</v>
@@ -3933,45 +3980,51 @@
         <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>301</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H38" t="s">
+        <v>301</v>
       </c>
       <c r="I38" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J38" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N38" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="O38" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="P38" t="s">
-        <v>296</v>
+        <v>304</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>305</v>
       </c>
       <c r="R38" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C39" t="s">
         <v>19</v>
@@ -3980,110 +4033,107 @@
         <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="F39" t="s">
         <v>6</v>
       </c>
       <c r="G39" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="H39" t="s">
+        <v>301</v>
+      </c>
+      <c r="I39" t="s">
+        <v>59</v>
+      </c>
+      <c r="J39" t="s">
+        <v>60</v>
+      </c>
+      <c r="K39" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" t="s">
+        <v>27</v>
+      </c>
+      <c r="N39" t="s">
+        <v>302</v>
+      </c>
+      <c r="O39" t="s">
+        <v>309</v>
+      </c>
+      <c r="P39" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>311</v>
+      </c>
+      <c r="R39" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>300</v>
       </c>
-      <c r="I39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J39" t="s">
-        <v>56</v>
-      </c>
-      <c r="K39" t="s">
-        <v>24</v>
-      </c>
-      <c r="L39" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" t="s">
+      <c r="B40" t="s">
+        <v>313</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
+        <v>314</v>
+      </c>
+      <c r="F40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" t="s">
+        <v>314</v>
+      </c>
+      <c r="H40" t="s">
         <v>301</v>
       </c>
-      <c r="O39" t="s">
-        <v>302</v>
-      </c>
-      <c r="P39" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>304</v>
-      </c>
-      <c r="R39" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="R40" s="2" t="s">
-        <v>310</v>
+      <c r="I40" t="s">
+        <v>59</v>
+      </c>
+      <c r="J40" t="s">
+        <v>60</v>
+      </c>
+      <c r="K40" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" t="s">
+        <v>26</v>
+      </c>
+      <c r="M40" t="s">
+        <v>27</v>
+      </c>
+      <c r="N40" t="s">
+        <v>315</v>
+      </c>
+      <c r="O40" t="s">
+        <v>316</v>
+      </c>
+      <c r="P40" t="s">
+        <v>317</v>
+      </c>
+      <c r="R40" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C41" t="s">
         <v>19</v>
@@ -4092,51 +4142,51 @@
         <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="F41" t="s">
         <v>7</v>
       </c>
       <c r="H41" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="I41" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J41" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N41" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="O41" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="P41" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="Q41" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="R41" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C42" t="s">
         <v>19</v>
@@ -4145,54 +4195,54 @@
         <v>20</v>
       </c>
       <c r="E42" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="F42" t="s">
         <v>6</v>
       </c>
       <c r="G42" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="H42" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="I42" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J42" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N42" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="O42" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="P42" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="Q42" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="R42" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C43" t="s">
         <v>19</v>
@@ -4201,51 +4251,51 @@
         <v>20</v>
       </c>
       <c r="E43" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="F43" t="s">
         <v>6</v>
       </c>
       <c r="G43" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="H43" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="I43" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J43" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K43" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N43" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="O43" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="P43" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="R43" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C44" t="s">
         <v>19</v>
@@ -4254,54 +4304,54 @@
         <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="F44" t="s">
         <v>6</v>
       </c>
       <c r="G44" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="H44" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="I44" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J44" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N44" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="O44" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="P44" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Q44" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="R44" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C45" t="s">
         <v>19</v>
@@ -4310,51 +4360,51 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F45" t="s">
         <v>6</v>
       </c>
       <c r="G45" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="H45" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="I45" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J45" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N45" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="O45" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="P45" t="s">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="R45" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
         <v>19</v>
@@ -4363,54 +4413,51 @@
         <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>121</v>
+        <v>351</v>
       </c>
       <c r="F46" t="s">
         <v>6</v>
       </c>
       <c r="G46" t="s">
-        <v>121</v>
+        <v>351</v>
       </c>
       <c r="H46" t="s">
-        <v>122</v>
+        <v>352</v>
       </c>
       <c r="I46" t="s">
-        <v>123</v>
+        <v>353</v>
       </c>
       <c r="J46" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="K46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N46" t="s">
-        <v>125</v>
+        <v>354</v>
       </c>
       <c r="O46" t="s">
-        <v>126</v>
+        <v>355</v>
       </c>
       <c r="P46" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>128</v>
+        <v>356</v>
       </c>
       <c r="R46" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C47" t="s">
         <v>19</v>
@@ -4419,54 +4466,54 @@
         <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="F47" t="s">
         <v>6</v>
       </c>
       <c r="G47" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="H47" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="I47" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="J47" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K47" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L47" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N47" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="O47" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="P47" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="Q47" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="R47" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C48" t="s">
         <v>19</v>
@@ -4475,54 +4522,54 @@
         <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="F48" t="s">
         <v>6</v>
       </c>
       <c r="G48" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H48" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="I48" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="J48" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="K48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N48" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="O48" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="P48" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="Q48" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="R48" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C49" t="s">
         <v>19</v>
@@ -4531,54 +4578,54 @@
         <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F49" t="s">
         <v>6</v>
       </c>
       <c r="G49" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H49" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="I49" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="J49" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K49" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N49" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="O49" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="P49" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="Q49" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="R49" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C50" t="s">
         <v>19</v>
@@ -4587,51 +4634,51 @@
         <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F50" t="s">
         <v>6</v>
       </c>
       <c r="G50" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="H50" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="I50" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J50" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K50" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N50" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="O50" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="P50" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="R50" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C51" t="s">
         <v>19</v>
@@ -4640,54 +4687,54 @@
         <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="F51" t="s">
         <v>6</v>
       </c>
       <c r="G51" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="H51" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="I51" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J51" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N51" t="s">
-        <v>383</v>
+        <v>61</v>
       </c>
       <c r="O51" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="P51" t="s">
-        <v>59</v>
+        <v>395</v>
       </c>
       <c r="Q51" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="R51" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="C52" t="s">
         <v>19</v>
@@ -4696,54 +4743,54 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="F52" t="s">
         <v>6</v>
       </c>
       <c r="G52" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="H52" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="I52" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J52" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K52" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L52" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N52" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="O52" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="P52" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="Q52" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="R52" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B53" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C53" t="s">
         <v>19</v>
@@ -4752,54 +4799,54 @@
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="F53" t="s">
         <v>6</v>
       </c>
       <c r="G53" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="H53" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="I53" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J53" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L53" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N53" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="O53" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="P53" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="Q53" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="R53" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="C54" t="s">
         <v>19</v>
@@ -4808,54 +4855,54 @@
         <v>20</v>
       </c>
       <c r="E54" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="F54" t="s">
         <v>6</v>
       </c>
       <c r="G54" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="H54" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="I54" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J54" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L54" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N54" t="s">
-        <v>404</v>
+        <v>321</v>
       </c>
       <c r="O54" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="P54" t="s">
-        <v>315</v>
+        <v>416</v>
       </c>
       <c r="Q54" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="R54" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C55" t="s">
         <v>19</v>
@@ -4864,54 +4911,54 @@
         <v>20</v>
       </c>
       <c r="E55" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="F55" t="s">
         <v>6</v>
       </c>
       <c r="G55" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="H55" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="I55" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J55" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N55" t="s">
-        <v>410</v>
+        <v>321</v>
       </c>
       <c r="O55" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="P55" t="s">
-        <v>315</v>
+        <v>422</v>
       </c>
       <c r="Q55" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="R55" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B56" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C56" t="s">
         <v>19</v>
@@ -4920,54 +4967,54 @@
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="F56" t="s">
         <v>6</v>
       </c>
       <c r="G56" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="H56" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="I56" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="J56" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="K56" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N56" t="s">
-        <v>417</v>
+        <v>289</v>
       </c>
       <c r="O56" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="P56" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="Q56" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="R56" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B57" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C57" t="s">
         <v>19</v>
@@ -4976,51 +5023,51 @@
         <v>20</v>
       </c>
       <c r="E57" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="F57" t="s">
         <v>7</v>
       </c>
       <c r="H57" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="I57" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J57" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K57" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N57" t="s">
-        <v>424</v>
+        <v>221</v>
       </c>
       <c r="O57" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="P57" t="s">
-        <v>218</v>
+        <v>435</v>
       </c>
       <c r="Q57" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="R57" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="C58" t="s">
         <v>19</v>
@@ -5029,107 +5076,107 @@
         <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="F58" t="s">
         <v>6</v>
       </c>
       <c r="G58" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="H58" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="I58" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J58" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K58" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N58" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="O58" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="P58" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="R58" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s">
+        <v>443</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>444</v>
+      </c>
+      <c r="F59" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" t="s">
+        <v>444</v>
+      </c>
+      <c r="H59" t="s">
         <v>433</v>
       </c>
-      <c r="C59" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" t="s">
-        <v>434</v>
-      </c>
-      <c r="F59" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" t="s">
-        <v>434</v>
-      </c>
-      <c r="H59" t="s">
-        <v>423</v>
-      </c>
       <c r="I59" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J59" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L59" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N59" t="s">
-        <v>435</v>
+        <v>221</v>
       </c>
       <c r="O59" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="P59" t="s">
-        <v>218</v>
+        <v>446</v>
       </c>
       <c r="Q59" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="R59" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="C60" t="s">
         <v>19</v>
@@ -5138,48 +5185,54 @@
         <v>20</v>
       </c>
       <c r="E60" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F60" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="G60" t="s">
+        <v>451</v>
+      </c>
+      <c r="H60" t="s">
+        <v>452</v>
       </c>
       <c r="I60" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="J60" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N60" t="s">
-        <v>442</v>
+        <v>140</v>
       </c>
       <c r="O60" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="P60" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="Q60" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="R60" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="C61" t="s">
         <v>19</v>
@@ -5188,51 +5241,51 @@
         <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="F61" t="s">
         <v>6</v>
       </c>
       <c r="G61" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="H61" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="I61" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="J61" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="K61" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N61" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="O61" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="P61" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="R61" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="B62" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="C62" t="s">
         <v>19</v>
@@ -5241,54 +5294,54 @@
         <v>20</v>
       </c>
       <c r="E62" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F62" t="s">
         <v>6</v>
       </c>
       <c r="G62" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="H62" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="I62" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="J62" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="K62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L62" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N62" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="O62" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="P62" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="Q62" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="R62" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="B63" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="C63" t="s">
         <v>19</v>
@@ -5297,51 +5350,54 @@
         <v>20</v>
       </c>
       <c r="E63" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="F63" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="G63" t="s">
+        <v>476</v>
       </c>
       <c r="H63" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="I63" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="J63" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="K63" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N63" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="O63" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="P63" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="Q63" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="R63" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B64" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C64" t="s">
         <v>19</v>
@@ -5350,54 +5406,48 @@
         <v>20</v>
       </c>
       <c r="E64" t="s">
-        <v>472</v>
+        <v>97</v>
       </c>
       <c r="F64" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" t="s">
-        <v>472</v>
-      </c>
-      <c r="H64" t="s">
-        <v>473</v>
+        <v>8</v>
       </c>
       <c r="I64" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J64" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L64" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N64" t="s">
-        <v>474</v>
+        <v>354</v>
       </c>
       <c r="O64" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="P64" t="s">
-        <v>96</v>
+        <v>485</v>
       </c>
       <c r="Q64" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="R64" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="C65" t="s">
         <v>19</v>
@@ -5406,54 +5456,54 @@
         <v>20</v>
       </c>
       <c r="E65" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="F65" t="s">
         <v>6</v>
       </c>
       <c r="G65" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="H65" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="I65" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J65" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K65" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N65" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="O65" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="P65" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="Q65" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="R65" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B66" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C66" t="s">
         <v>19</v>
@@ -5462,54 +5512,54 @@
         <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>487</v>
+        <v>227</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
       </c>
       <c r="G66" t="s">
-        <v>487</v>
+        <v>227</v>
       </c>
       <c r="H66" t="s">
-        <v>488</v>
+        <v>220</v>
       </c>
       <c r="I66" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J66" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L66" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M66" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N66" t="s">
-        <v>489</v>
+        <v>28</v>
       </c>
       <c r="O66" t="s">
-        <v>490</v>
+        <v>221</v>
       </c>
       <c r="P66" t="s">
-        <v>491</v>
+        <v>228</v>
       </c>
       <c r="Q66" t="s">
-        <v>492</v>
+        <v>230</v>
       </c>
       <c r="R66" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B67" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C67" t="s">
         <v>19</v>
@@ -5518,54 +5568,54 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="F67" t="s">
         <v>6</v>
       </c>
       <c r="G67" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="H67" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="I67" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J67" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K67" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N67" t="s">
-        <v>474</v>
+        <v>99</v>
       </c>
       <c r="O67" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="P67" t="s">
-        <v>96</v>
+        <v>502</v>
       </c>
       <c r="Q67" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="R67" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B68" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="C68" t="s">
         <v>19</v>
@@ -5574,54 +5624,54 @@
         <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
       </c>
       <c r="G68" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="H68" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="I68" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J68" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M68" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N68" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="O68" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="P68" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="Q68" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="R68" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="C69" t="s">
         <v>19</v>
@@ -5630,46 +5680,46 @@
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F69" t="s">
         <v>6</v>
       </c>
       <c r="G69" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="H69" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="I69" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J69" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N69" t="s">
         <v>508</v>
       </c>
       <c r="O69" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="P69" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="Q69" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="R69" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
